--- a/data/b2_primavera/B2 Primavera 06-2026.xlsx
+++ b/data/b2_primavera/B2 Primavera 06-2026.xlsx
@@ -4833,25 +4833,25 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>58517.73</v>
+        <v>57751.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>3398.41</v>
+        <v>1213.55</v>
       </c>
     </row>
     <row r="4">
@@ -4869,25 +4869,25 @@
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>3934.69</v>
+        <v>4071.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>14000</v>
+        <v>1233.09</v>
       </c>
     </row>
     <row r="6">
@@ -4896,16 +4896,16 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1465.22</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="7">
@@ -4914,88 +4914,88 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3600</v>
+        <v>2435.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46185</v>
+        <v>46183</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1086.53</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46187</v>
+        <v>46185</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>3572.77</v>
+        <v>1208.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>9310.6</v>
+        <v>1264.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46188</v>
+        <v>46187</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1759.72</v>
+        <v>3570.21</v>
       </c>
     </row>
     <row r="12">
@@ -5004,34 +5004,34 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3532.11</v>
+        <v>9157.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>1013.91</v>
+        <v>2877.79</v>
       </c>
     </row>
     <row r="14">
@@ -5040,34 +5040,34 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Campanha contra a concorrência nova</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>6500</v>
+        <v>3250.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46193</v>
+        <v>46191</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Campanha contra a concorrência nova</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>20542.35</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="16">
@@ -5076,16 +5076,16 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1696.35</v>
+        <v>20297.46</v>
       </c>
     </row>
     <row r="17">
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3634.44</v>
+        <v>3941.1</v>
       </c>
     </row>
     <row r="18">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>3847.53</v>
+        <v>3779.29</v>
       </c>
     </row>
     <row r="19">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>1007.11</v>
+        <v>1065.59</v>
       </c>
     </row>
   </sheetData>
